--- a/data/trans_dic/Q23_tabaco_R2-Edad-trans_dic.xlsx
+++ b/data/trans_dic/Q23_tabaco_R2-Edad-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población cuyo inicio en el consumo de tabaco fue antes de los 15 años</t>
+          <t>Población cuyo inicio en el consumo de tabaco fue antes de los 15 años (tasa de respuesta: 95,12%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>33,79; 48,99</t>
+          <t>34,51; 49,21</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>35,77; 51,65</t>
+          <t>35,81; 52,03</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>33,76; 49,7</t>
+          <t>33,91; 50,3</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>19,58; 56,77</t>
+          <t>21,1; 56,3</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>35,68; 50,67</t>
+          <t>36,05; 51,19</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>45,26; 60,84</t>
+          <t>44,71; 60,94</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>40,05; 57,57</t>
+          <t>39,58; 56,76</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>19,92; 49,26</t>
+          <t>20,09; 48,31</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>36,87; 47,38</t>
+          <t>37,34; 47,52</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>43,11; 54,53</t>
+          <t>43,26; 54,55</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>38,67; 50,64</t>
+          <t>38,66; 50,26</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>25,03; 50,03</t>
+          <t>26,78; 49,45</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>24,29; 33,63</t>
+          <t>24,09; 34,26</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>23,83; 33,21</t>
+          <t>23,8; 33,57</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>26,02; 36,78</t>
+          <t>25,96; 36,73</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>20,6; 37,89</t>
+          <t>20,9; 38,69</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>21,49; 32,52</t>
+          <t>21,17; 32,28</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>19,98; 30,27</t>
+          <t>20,21; 30,18</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>26,61; 37,65</t>
+          <t>26,35; 37,43</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>17,79; 32,64</t>
+          <t>18,88; 33,71</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>24,18; 31,36</t>
+          <t>24,33; 31,39</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>23,78; 30,83</t>
+          <t>23,63; 30,71</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>27,65; 35,01</t>
+          <t>27,45; 35,11</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>22,14; 33,49</t>
+          <t>21,96; 33,25</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>23,47; 32,76</t>
+          <t>23,48; 32,93</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>26,38; 35,65</t>
+          <t>26,82; 35,48</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>25,4; 36,14</t>
+          <t>25,49; 36,48</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>24,85; 39,33</t>
+          <t>24,69; 38,36</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>20,93; 31,37</t>
+          <t>20,7; 30,79</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>22,29; 32,06</t>
+          <t>21,96; 31,96</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>20,76; 30,94</t>
+          <t>21,05; 31,61</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>16,83; 26,69</t>
+          <t>16,86; 26,28</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>23,93; 30,87</t>
+          <t>23,67; 30,09</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>26,27; 32,74</t>
+          <t>25,98; 32,82</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>24,8; 32,07</t>
+          <t>25,0; 31,92</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>22,58; 31,16</t>
+          <t>22,61; 31,3</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>29,07; 40,18</t>
+          <t>29,25; 40,29</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>31,16; 41,07</t>
+          <t>30,92; 40,73</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>29,84; 39,92</t>
+          <t>29,75; 40,14</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4,53; 30,02</t>
+          <t>4,54; 29,08</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>12,9; 24,22</t>
+          <t>13,52; 24,98</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>20,99; 31,41</t>
+          <t>20,9; 31,46</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>14,85; 24,48</t>
+          <t>15,18; 24,33</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>18,62; 27,07</t>
+          <t>18,47; 26,85</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>24,39; 32,86</t>
+          <t>24,79; 32,99</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>28,54; 35,56</t>
+          <t>28,36; 35,62</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>24,74; 31,67</t>
+          <t>24,71; 31,48</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>6,88; 26,25</t>
+          <t>7,44; 26,37</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>35,84; 49,49</t>
+          <t>36,41; 49,51</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>33,3; 45,24</t>
+          <t>33,64; 45,72</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>32,95; 45,83</t>
+          <t>32,99; 45,32</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>30,98; 41,31</t>
+          <t>31,51; 41,43</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>5,04; 23,44</t>
+          <t>5,1; 22,94</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,59; 18,85</t>
+          <t>7,22; 20,27</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>14,89; 28,62</t>
+          <t>15,02; 28,68</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>20,98; 29,98</t>
+          <t>21,73; 30,84</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>30,84; 42,25</t>
+          <t>31,02; 42,35</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>26,21; 36,28</t>
+          <t>26,82; 36,55</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>27,53; 36,89</t>
+          <t>27,17; 36,9</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>28,89; 35,83</t>
+          <t>28,77; 35,68</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>32,51; 47,71</t>
+          <t>32,46; 48,31</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>33,57; 47,92</t>
+          <t>33,78; 48,4</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>35,19; 50,39</t>
+          <t>35,3; 51,01</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>32,87; 43,7</t>
+          <t>33,32; 43,89</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 20,75</t>
+          <t>0,0; 27,48</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>3,6; 37,76</t>
+          <t>3,56; 35,72</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1,83; 16,98</t>
+          <t>1,84; 16,71</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>16,69; 30,1</t>
+          <t>16,84; 29,26</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>29,44; 44,25</t>
+          <t>29,01; 43,74</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>30,95; 44,69</t>
+          <t>31,01; 44,4</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>28,59; 41,37</t>
+          <t>28,0; 40,48</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>29,8; 38,37</t>
+          <t>29,62; 38,03</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>43,26; 60,94</t>
+          <t>42,48; 59,79</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>37,71; 53,79</t>
+          <t>38,14; 54,33</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>36,58; 51,89</t>
+          <t>36,36; 53,1</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>35,9; 50,82</t>
+          <t>36,6; 50,26</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 58,84</t>
+          <t>8,84; 67,25</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0; 18,74</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0; 20,75</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>5,26; 29,82</t>
+          <t>5,22; 29,6</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>40,71; 57,87</t>
+          <t>41,37; 58,44</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>35,14; 50,24</t>
+          <t>35,14; 51,37</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>33,55; 48,46</t>
+          <t>34,07; 49,03</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>33,26; 45,84</t>
+          <t>33,49; 45,89</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>33,03; 37,64</t>
+          <t>33,25; 37,82</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>33,61; 37,95</t>
+          <t>33,75; 38,17</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>33,85; 38,42</t>
+          <t>33,83; 38,54</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>17,86; 34,95</t>
+          <t>17,78; 35,22</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>23,71; 29,28</t>
+          <t>23,53; 29,28</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>25,13; 30,47</t>
+          <t>25,15; 30,56</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>23,54; 28,6</t>
+          <t>23,4; 28,61</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>21,81; 26,61</t>
+          <t>21,64; 26,7</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>30,04; 33,72</t>
+          <t>30,17; 33,8</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>30,83; 34,21</t>
+          <t>30,97; 34,39</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>29,97; 33,66</t>
+          <t>30,03; 33,63</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>19,82; 30,86</t>
+          <t>19,29; 30,68</t>
         </is>
       </c>
     </row>
@@ -1810,7 +1810,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población cuyo inicio en el consumo de tabaco fue antes de los 15 años</t>
+          <t>Población cuyo inicio en el consumo de tabaco fue antes de los 15 años (tasa de respuesta: 95,12%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2068,62 +2068,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>57126; 82836</t>
+          <t>58342; 83195</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>55745; 80497</t>
+          <t>55811; 81084</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>50129; 73810</t>
+          <t>50357; 74699</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>19114; 55423</t>
+          <t>20598; 54966</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>57239; 81280</t>
+          <t>57823; 82115</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>70188; 94342</t>
+          <t>69328; 94491</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>48674; 69961</t>
+          <t>48097; 68975</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>15553; 38457</t>
+          <t>15682; 37720</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>121475; 156105</t>
+          <t>123046; 156577</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>134024; 169534</t>
+          <t>134491; 169599</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>104409; 136742</t>
+          <t>104401; 135729</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>43984; 87905</t>
+          <t>47052; 86894</t>
         </is>
       </c>
     </row>
@@ -2276,62 +2276,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>88452; 122467</t>
+          <t>87729; 124764</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>87242; 121557</t>
+          <t>87127; 122886</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>79010; 111676</t>
+          <t>78833; 111537</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>34535; 63539</t>
+          <t>35044; 64879</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>55637; 84208</t>
+          <t>54810; 83564</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>64760; 98110</t>
+          <t>65494; 97799</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>69901; 98906</t>
+          <t>69223; 98323</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>25877; 47486</t>
+          <t>27465; 49041</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>150656; 195379</t>
+          <t>151590; 195565</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>164124; 212760</t>
+          <t>163098; 211937</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>156612; 198282</t>
+          <t>155455; 198863</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>69333; 104867</t>
+          <t>68767; 104115</t>
         </is>
       </c>
     </row>
@@ -2484,62 +2484,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>88011; 122842</t>
+          <t>88051; 123499</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>110003; 148629</t>
+          <t>111835; 147939</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>85411; 121504</t>
+          <t>85698; 122651</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>47001; 74382</t>
+          <t>46702; 72553</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>62465; 93619</t>
+          <t>61789; 91914</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>79900; 114932</t>
+          <t>78731; 114548</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>62855; 93696</t>
+          <t>63748; 95719</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>31381; 49773</t>
+          <t>31452; 49016</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>161158; 207889</t>
+          <t>159428; 202685</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>203692; 253880</t>
+          <t>201462; 254488</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>158515; 204948</t>
+          <t>159782; 203993</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>84830; 117051</t>
+          <t>84913; 117586</t>
         </is>
       </c>
     </row>
@@ -2692,62 +2692,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>93363; 129056</t>
+          <t>93950; 129427</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>137885; 181755</t>
+          <t>136856; 180232</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>114990; 153858</t>
+          <t>114637; 154698</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>24098; 159679</t>
+          <t>24159; 154645</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>24460; 45923</t>
+          <t>25636; 47356</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>67871; 101538</t>
+          <t>67560; 101690</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>46785; 77113</t>
+          <t>47837; 76644</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>45880; 66698</t>
+          <t>45504; 66152</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>124607; 167858</t>
+          <t>126635; 168525</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>218552; 272351</t>
+          <t>217180; 272785</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>173281; 221845</t>
+          <t>173098; 220515</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>53530; 204295</t>
+          <t>57907; 205247</t>
         </is>
       </c>
     </row>
@@ -2900,62 +2900,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>81405; 112423</t>
+          <t>82707; 112470</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>96479; 131088</t>
+          <t>97464; 132478</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>92255; 128298</t>
+          <t>92365; 126889</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>101971; 135970</t>
+          <t>103708; 136371</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>2977; 13833</t>
+          <t>3009; 13540</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>7739; 22128</t>
+          <t>8471; 23788</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>26032; 50030</t>
+          <t>26258; 50127</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>42761; 61099</t>
+          <t>44281; 62845</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>88264; 120917</t>
+          <t>88777; 121178</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>106709; 147683</t>
+          <t>109175; 148819</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>125189; 167777</t>
+          <t>123538; 167826</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>153959; 190939</t>
+          <t>153306; 190154</t>
         </is>
       </c>
     </row>
@@ -3108,62 +3108,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>46998; 68976</t>
+          <t>46918; 69832</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>71141; 101559</t>
+          <t>71586; 102573</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>64944; 92987</t>
+          <t>65148; 94139</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>72502; 96376</t>
+          <t>73478; 96791</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0; 3754</t>
+          <t>0; 4972</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1033; 10849</t>
+          <t>1022; 10262</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>1034; 9600</t>
+          <t>1039; 9448</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>15211; 27438</t>
+          <t>15354; 26674</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>47884; 71980</t>
+          <t>47189; 71152</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>74475; 107540</t>
+          <t>74621; 106848</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>68939; 99738</t>
+          <t>67496; 97599</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>92889; 119613</t>
+          <t>92329; 118550</t>
         </is>
       </c>
     </row>
@@ -3316,62 +3316,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>51848; 73036</t>
+          <t>50911; 71663</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>60823; 86759</t>
+          <t>61519; 87633</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>47768; 67746</t>
+          <t>47471; 69328</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>47973; 67910</t>
+          <t>48906; 67174</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>0; 8160</t>
+          <t>1225; 9326</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>0; 1955</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>0; 2292</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>1173; 6643</t>
+          <t>1163; 6593</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>54438; 77386</t>
+          <t>55325; 78151</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>60348; 86282</t>
+          <t>60349; 88211</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>47509; 68625</t>
+          <t>48252; 69431</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>51851; 71478</t>
+          <t>52219; 71545</t>
         </is>
       </c>
     </row>
@@ -3524,62 +3524,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>568525; 647867</t>
+          <t>572225; 650850</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>687193; 775790</t>
+          <t>689918; 780342</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>598752; 679504</t>
+          <t>598347; 681670</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>298145; 583493</t>
+          <t>296898; 587979</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>236687; 292305</t>
+          <t>234941; 292311</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>331091; 401390</t>
+          <t>331337; 402629</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>292931; 355893</t>
+          <t>291263; 356031</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>212404; 259085</t>
+          <t>210736; 259962</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>816937; 916984</t>
+          <t>820550; 919160</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>1036339; 1150041</t>
+          <t>1041138; 1156243</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>903152; 1014274</t>
+          <t>904954; 1013420</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>523840; 815602</t>
+          <t>509845; 811062</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/Q23_tabaco_R2-Edad-trans_dic.xlsx
+++ b/data/trans_dic/Q23_tabaco_R2-Edad-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>39,49%</t>
+          <t>36,3%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>33,75%</t>
+          <t>30,85%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>36,94%</t>
+          <t>33,73%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>34,51; 49,21</t>
+          <t>33,43; 49,25</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>35,81; 52,03</t>
+          <t>36,68; 51,92</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>33,91; 50,3</t>
+          <t>33,45; 49,36</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>21,1; 56,3</t>
+          <t>21,46; 53,6</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>36,05; 51,19</t>
+          <t>35,95; 50,77</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>44,71; 60,94</t>
+          <t>45,5; 61,25</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>39,58; 56,76</t>
+          <t>39,81; 57,17</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>20,09; 48,31</t>
+          <t>18,74; 46,14</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>37,34; 47,52</t>
+          <t>36,81; 47,6</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>43,26; 54,55</t>
+          <t>43,32; 54,88</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>38,66; 50,26</t>
+          <t>38,61; 50,65</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>26,78; 49,45</t>
+          <t>24,02; 46,15</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>28,91%</t>
+          <t>28,74%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>25,58%</t>
+          <t>24,7%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>27,36%</t>
+          <t>26,9%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>24,09; 34,26</t>
+          <t>24,59; 33,74</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>23,8; 33,57</t>
+          <t>24,17; 33,55</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>25,96; 36,73</t>
+          <t>26,08; 37,08</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>20,9; 38,69</t>
+          <t>21,15; 36,83</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>21,17; 32,28</t>
+          <t>21,27; 31,89</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>20,21; 30,18</t>
+          <t>20,78; 30,55</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>26,35; 37,43</t>
+          <t>26,57; 37,62</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>18,88; 33,71</t>
+          <t>18,32; 32,69</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>24,33; 31,39</t>
+          <t>24,47; 31,37</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>23,63; 30,71</t>
+          <t>23,36; 30,51</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>27,45; 35,11</t>
+          <t>27,69; 35,54</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>21,96; 33,25</t>
+          <t>21,06; 32,36</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>31,58%</t>
+          <t>30,54%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>21,45%</t>
+          <t>21,06%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>26,55%</t>
+          <t>25,93%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>23,48; 32,93</t>
+          <t>23,64; 32,9</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>26,82; 35,48</t>
+          <t>26,73; 36,0</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>25,49; 36,48</t>
+          <t>25,74; 35,81</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>24,69; 38,36</t>
+          <t>24,02; 37,57</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>20,7; 30,79</t>
+          <t>20,99; 31,31</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>21,96; 31,96</t>
+          <t>22,05; 31,84</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>21,05; 31,61</t>
+          <t>21,03; 30,81</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>16,86; 26,28</t>
+          <t>16,55; 26,16</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>23,67; 30,09</t>
+          <t>23,73; 30,66</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>25,98; 32,82</t>
+          <t>25,81; 32,62</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>25,0; 31,92</t>
+          <t>25,26; 32,02</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>22,61; 31,3</t>
+          <t>21,9; 30,28</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>15,07%</t>
+          <t>28,41%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>22,5%</t>
+          <t>21,98%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>17,42%</t>
+          <t>25,45%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>29,25; 40,29</t>
+          <t>28,96; 40,36</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>30,92; 40,73</t>
+          <t>30,68; 40,65</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>29,75; 40,14</t>
+          <t>29,97; 39,93</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4,54; 29,08</t>
+          <t>23,37; 34,37</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>13,52; 24,98</t>
+          <t>13,22; 24,53</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>20,9; 31,46</t>
+          <t>20,56; 31,78</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>15,18; 24,33</t>
+          <t>14,95; 23,67</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>18,47; 26,85</t>
+          <t>18,05; 26,12</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>24,79; 32,99</t>
+          <t>24,68; 32,39</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>28,36; 35,62</t>
+          <t>28,46; 35,3</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>24,71; 31,48</t>
+          <t>24,44; 31,69</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>7,44; 26,37</t>
+          <t>22,29; 28,99</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>35,99%</t>
+          <t>35,33%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>25,49%</t>
+          <t>24,76%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>31,98%</t>
+          <t>31,22%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>36,41; 49,51</t>
+          <t>36,39; 49,69</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>33,64; 45,72</t>
+          <t>32,95; 45,45</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>32,99; 45,32</t>
+          <t>33,46; 46,26</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>31,51; 41,43</t>
+          <t>30,41; 40,2</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>5,1; 22,94</t>
+          <t>5,12; 22,45</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,22; 20,27</t>
+          <t>7,18; 19,98</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>15,02; 28,68</t>
+          <t>14,76; 28,31</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>21,73; 30,84</t>
+          <t>20,64; 29,55</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>31,02; 42,35</t>
+          <t>31,1; 42,69</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>26,82; 36,55</t>
+          <t>26,87; 36,32</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>27,17; 36,9</t>
+          <t>27,91; 37,0</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>28,77; 35,68</t>
+          <t>27,44; 34,84</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>38,41%</t>
+          <t>37,56%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>22,76%</t>
+          <t>23,26%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>33,83%</t>
+          <t>33,39%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>32,46; 48,31</t>
+          <t>32,73; 48,17</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>33,78; 48,4</t>
+          <t>33,4; 47,75</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>35,3; 51,01</t>
+          <t>34,9; 49,95</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>33,32; 43,89</t>
+          <t>31,54; 42,31</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 27,48</t>
+          <t>0,0; 25,21</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>3,56; 35,72</t>
+          <t>5,94; 37,55</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1,84; 16,71</t>
+          <t>1,84; 16,58</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>16,84; 29,26</t>
+          <t>17,52; 29,64</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>29,01; 43,74</t>
+          <t>28,86; 43,26</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>31,01; 44,4</t>
+          <t>31,29; 44,82</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>28,0; 40,48</t>
+          <t>27,55; 40,68</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>29,62; 38,03</t>
+          <t>29,36; 37,73</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>43,33%</t>
+          <t>42,24%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>14,9%</t>
+          <t>14,43%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>39,27%</t>
+          <t>38,24%</t>
         </is>
       </c>
     </row>
@@ -1557,27 +1557,27 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>42,48; 59,79</t>
+          <t>43,71; 60,98</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>38,14; 54,33</t>
+          <t>37,8; 54,44</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>36,36; 53,1</t>
+          <t>36,28; 51,73</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>36,6; 50,26</t>
+          <t>35,08; 49,62</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>8,84; 67,25</t>
+          <t>9,21; 65,87</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -1592,27 +1592,27 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>5,22; 29,6</t>
+          <t>5,98; 27,37</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>41,37; 58,44</t>
+          <t>41,66; 59,06</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>35,14; 51,37</t>
+          <t>35,55; 50,66</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>34,07; 49,03</t>
+          <t>33,01; 48,81</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>33,49; 45,89</t>
+          <t>32,72; 44,55</t>
         </is>
       </c>
     </row>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>29,23%</t>
+          <t>33,56%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>24,14%</t>
+          <t>23,47%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>27,35%</t>
+          <t>29,47%</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>33,25; 37,82</t>
+          <t>32,97; 37,95</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>33,75; 38,17</t>
+          <t>33,81; 38,15</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>33,83; 38,54</t>
+          <t>33,72; 38,39</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>17,78; 35,22</t>
+          <t>31,06; 36,06</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>23,53; 29,28</t>
+          <t>23,52; 29,05</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>25,15; 30,56</t>
+          <t>25,16; 30,37</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>23,4; 28,61</t>
+          <t>23,78; 28,72</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>21,64; 26,7</t>
+          <t>21,14; 25,94</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>30,17; 33,8</t>
+          <t>30,22; 33,88</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>30,97; 34,39</t>
+          <t>31,09; 34,5</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>30,03; 33,63</t>
+          <t>30,16; 33,69</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>19,29; 30,68</t>
+          <t>27,68; 31,11</t>
         </is>
       </c>
     </row>
@@ -2015,7 +2015,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>38550</t>
+          <t>35492</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2035,7 +2035,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>26355</t>
+          <t>26889</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -2055,7 +2055,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>64905</t>
+          <t>62381</t>
         </is>
       </c>
     </row>
@@ -2068,62 +2068,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>58342; 83195</t>
+          <t>56522; 83270</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>55811; 81084</t>
+          <t>57159; 80910</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>50357; 74699</t>
+          <t>49671; 73299</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>20598; 54966</t>
+          <t>20984; 52406</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>57823; 82115</t>
+          <t>57661; 81434</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>69328; 94491</t>
+          <t>70561; 94973</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>48097; 68975</t>
+          <t>48376; 69481</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>15682; 37720</t>
+          <t>16330; 40215</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>123046; 156577</t>
+          <t>121294; 156825</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>134491; 169599</t>
+          <t>134683; 170636</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>104401; 135729</t>
+          <t>104246; 136776</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>47052; 86894</t>
+          <t>44416; 85345</t>
         </is>
       </c>
     </row>
@@ -2223,7 +2223,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>48471</t>
+          <t>53840</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2243,7 +2243,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>37217</t>
+          <t>38558</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2263,7 +2263,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>85688</t>
+          <t>92398</t>
         </is>
       </c>
     </row>
@@ -2276,62 +2276,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>87729; 124764</t>
+          <t>89552; 122872</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>87127; 122886</t>
+          <t>88472; 122792</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>78833; 111537</t>
+          <t>79179; 112583</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>35044; 64879</t>
+          <t>39619; 69003</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>54810; 83564</t>
+          <t>55067; 82555</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>65494; 97799</t>
+          <t>67339; 99021</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>69223; 98323</t>
+          <t>69784; 98817</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>27465; 49041</t>
+          <t>28603; 51033</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>151590; 195565</t>
+          <t>152493; 195456</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>163098; 211937</t>
+          <t>161191; 210587</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>155455; 198863</t>
+          <t>156795; 201259</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>68767; 104115</t>
+          <t>72322; 111155</t>
         </is>
       </c>
     </row>
@@ -2431,7 +2431,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>59727</t>
+          <t>64742</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2451,7 +2451,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>40007</t>
+          <t>42273</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>99734</t>
+          <t>107015</t>
         </is>
       </c>
     </row>
@@ -2484,62 +2484,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>88051; 123499</t>
+          <t>88670; 123373</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>111835; 147939</t>
+          <t>111449; 150111</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>85698; 122651</t>
+          <t>86551; 120423</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>46702; 72553</t>
+          <t>50923; 79632</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>61789; 91914</t>
+          <t>62663; 93450</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>78731; 114548</t>
+          <t>79031; 114140</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>63748; 95719</t>
+          <t>63691; 93286</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>31452; 49016</t>
+          <t>33213; 52506</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>159428; 202685</t>
+          <t>159804; 206481</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>201462; 254488</t>
+          <t>200159; 252949</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>159782; 203993</t>
+          <t>161458; 204642</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>84913; 117586</t>
+          <t>90377; 124957</t>
         </is>
       </c>
     </row>
@@ -2639,7 +2639,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>80135</t>
+          <t>87722</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2659,7 +2659,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>55453</t>
+          <t>57851</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2679,7 +2679,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>135588</t>
+          <t>145573</t>
         </is>
       </c>
     </row>
@@ -2692,62 +2692,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>93950; 129427</t>
+          <t>93008; 129645</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>136856; 180232</t>
+          <t>135761; 179889</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>114637; 154698</t>
+          <t>115496; 153865</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>24159; 154645</t>
+          <t>72157; 106111</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>25636; 47356</t>
+          <t>25073; 46514</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>67560; 101690</t>
+          <t>66454; 102741</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>47837; 76644</t>
+          <t>47093; 74574</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>45504; 66152</t>
+          <t>47520; 68762</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>126635; 168525</t>
+          <t>126082; 165439</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>217180; 272785</t>
+          <t>217954; 270331</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>173098; 220515</t>
+          <t>171166; 221943</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>57907; 205247</t>
+          <t>127510; 165792</t>
         </is>
       </c>
     </row>
@@ -2847,7 +2847,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>118469</t>
+          <t>124230</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2867,7 +2867,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>51959</t>
+          <t>55521</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2887,7 +2887,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>170428</t>
+          <t>179751</t>
         </is>
       </c>
     </row>
@@ -2900,62 +2900,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>82707; 112470</t>
+          <t>82658; 112860</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>97464; 132478</t>
+          <t>95474; 131681</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>92365; 126889</t>
+          <t>93666; 129522</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>103708; 136371</t>
+          <t>106933; 141357</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>3009; 13540</t>
+          <t>3020; 13251</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>8471; 23788</t>
+          <t>8423; 23447</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>26258; 50127</t>
+          <t>25801; 49490</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>44281; 62845</t>
+          <t>46282; 66269</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>88777; 121178</t>
+          <t>89005; 122176</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>109175; 148819</t>
+          <t>109404; 147866</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>123538; 167826</t>
+          <t>126914; 168272</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>153306; 190154</t>
+          <t>158022; 200653</t>
         </is>
       </c>
     </row>
@@ -3055,7 +3055,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>84706</t>
+          <t>90993</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -3075,7 +3075,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>20749</t>
+          <t>23216</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -3095,7 +3095,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>105455</t>
+          <t>114209</t>
         </is>
       </c>
     </row>
@@ -3108,62 +3108,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>46918; 69832</t>
+          <t>47313; 69635</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>71586; 102573</t>
+          <t>70788; 101183</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>65148; 94139</t>
+          <t>64405; 92184</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>73478; 96791</t>
+          <t>76422; 102497</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0; 4972</t>
+          <t>0; 4561</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1022; 10262</t>
+          <t>1706; 10790</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>1039; 9448</t>
+          <t>1040; 9379</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>15354; 26674</t>
+          <t>17488; 29586</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>47189; 71152</t>
+          <t>46938; 70362</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>74621; 106848</t>
+          <t>75304; 107867</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>67496; 97599</t>
+          <t>66420; 98075</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>92329; 118550</t>
+          <t>100444; 129059</t>
         </is>
       </c>
     </row>
@@ -3263,7 +3263,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>57911</t>
+          <t>61987</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3283,7 +3283,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>3320</t>
+          <t>3554</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3303,7 +3303,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>61231</t>
+          <t>65540</t>
         </is>
       </c>
     </row>
@@ -3316,27 +3316,27 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>50911; 71663</t>
+          <t>52388; 73083</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>61519; 87633</t>
+          <t>60973; 87809</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>47471; 69328</t>
+          <t>47376; 67545</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>48906; 67174</t>
+          <t>51476; 72821</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>1225; 9326</t>
+          <t>1277; 9135</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
@@ -3351,27 +3351,27 @@
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>1163; 6593</t>
+          <t>1472; 6742</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>55325; 78151</t>
+          <t>55706; 78981</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>60349; 88211</t>
+          <t>61050; 86987</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>48252; 69431</t>
+          <t>46741; 69119</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>52219; 71545</t>
+          <t>56085; 76357</t>
         </is>
       </c>
     </row>
@@ -3471,7 +3471,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>487969</t>
+          <t>519004</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3491,7 +3491,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>235060</t>
+          <t>247863</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>723029</t>
+          <t>766867</t>
         </is>
       </c>
     </row>
@@ -3524,62 +3524,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>572225; 650850</t>
+          <t>567441; 653171</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>689918; 780342</t>
+          <t>691164; 779873</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>598347; 681670</t>
+          <t>596422; 678993</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>296898; 587979</t>
+          <t>480345; 557676</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>234941; 292311</t>
+          <t>234847; 290074</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>331337; 402629</t>
+          <t>331478; 400047</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>291263; 356031</t>
+          <t>295955; 357459</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>210736; 259962</t>
+          <t>223224; 273858</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>820550; 919160</t>
+          <t>821881; 921289</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>1041138; 1156243</t>
+          <t>1045128; 1159739</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>904954; 1013420</t>
+          <t>908851; 1015207</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>509845; 811062</t>
+          <t>720426; 809577</t>
         </is>
       </c>
     </row>
